--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
@@ -13,7 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$B10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Revenue'!$A1:$N6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Revenue'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Revenue'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Personnel'!$A1:$N5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Personnel'!$1:$1</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Annual Fundraising</t>
+  </si>
+  <si>
+    <t>Scholarship Discount</t>
   </si>
   <si>
     <t>TOTAL REVENUE</t>
@@ -716,7 +719,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -948,61 +951,106 @@
         <v>4167</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="8">
-        <f>SUM(B2:B5)</f>
+      <c r="B6" s="7">
+        <v>1</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7">
+        <v>0</v>
+      </c>
+      <c r="N6" s="7">
+        <f>SUM(B6:M6)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="8">
+        <f>SUM(B2:B6)</f>
         <v>155900</v>
       </c>
-      <c r="C6" s="8">
-        <f>SUM(C2:C5)</f>
-        <v>8900</v>
-      </c>
-      <c r="D6" s="8">
-        <f>SUM(D2:D5)</f>
-        <v>8900</v>
-      </c>
-      <c r="E6" s="8">
-        <f>SUM(E2:E5)</f>
-        <v>8900</v>
-      </c>
-      <c r="F6" s="8">
-        <f>SUM(F2:F5)</f>
-        <v>8900</v>
-      </c>
-      <c r="G6" s="8">
-        <f>SUM(G2:G5)</f>
-        <v>8900</v>
-      </c>
-      <c r="H6" s="8">
-        <f>SUM(H2:H5)</f>
-        <v>8900</v>
-      </c>
-      <c r="I6" s="8">
-        <f>SUM(I2:I5)</f>
-        <v>8900</v>
-      </c>
-      <c r="J6" s="8">
-        <f>SUM(J2:J5)</f>
-        <v>8900</v>
-      </c>
-      <c r="K6" s="8">
-        <f>SUM(K2:K5)</f>
-        <v>8900</v>
-      </c>
-      <c r="L6" s="8" t="str">
-        <f>SUM(L2:L5)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="8" t="str">
-        <f>SUM(M2:M5)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="8">
-        <f>SUM(B6:M6)</f>
-        <v>236000</v>
+      <c r="C7" s="8">
+        <f>SUM(C2:C6)</f>
+        <v>7460</v>
+      </c>
+      <c r="D7" s="8">
+        <f>SUM(D2:D6)</f>
+        <v>7460</v>
+      </c>
+      <c r="E7" s="8">
+        <f>SUM(E2:E6)</f>
+        <v>7460</v>
+      </c>
+      <c r="F7" s="8">
+        <f>SUM(F2:F6)</f>
+        <v>7460</v>
+      </c>
+      <c r="G7" s="8">
+        <f>SUM(G2:G6)</f>
+        <v>7460</v>
+      </c>
+      <c r="H7" s="8">
+        <f>SUM(H2:H6)</f>
+        <v>7460</v>
+      </c>
+      <c r="I7" s="8">
+        <f>SUM(I2:I6)</f>
+        <v>7460</v>
+      </c>
+      <c r="J7" s="8">
+        <f>SUM(J2:J6)</f>
+        <v>7460</v>
+      </c>
+      <c r="K7" s="8">
+        <f>SUM(K2:K6)</f>
+        <v>7460</v>
+      </c>
+      <c r="L7" s="8">
+        <f>SUM(L2:L6)</f>
+        <v>-1440</v>
+      </c>
+      <c r="M7" s="8" t="str">
+        <f>SUM(M2:M6)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <f>SUM(B7:M7)</f>
+        <v>221600</v>
       </c>
     </row>
   </sheetData>
@@ -1074,7 +1122,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B2" s="7">
         <v>131313</v>
@@ -1119,7 +1167,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="7">
         <v>107438</v>
@@ -1164,7 +1212,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B4" s="7">
         <v>10092</v>
@@ -1209,7 +1257,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="8" t="str">
         <f>SUM(B2:B4)</f>
@@ -1333,7 +1381,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="7">
         <v>2500</v>
@@ -1378,7 +1426,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="7">
         <v>300</v>
@@ -1423,7 +1471,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="7">
         <v>200</v>
@@ -1468,7 +1516,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="7">
         <v>500</v>
@@ -1513,7 +1561,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="7">
         <v>300</v>
@@ -1558,7 +1606,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="7">
         <v>250</v>
@@ -1603,7 +1651,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="8" t="str">
         <f>SUM(B2:B7)</f>
@@ -1727,64 +1775,64 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" s="10">
-        <f>Revenue!B6</f>
+        <f>Revenue!B7</f>
         <v>155900</v>
       </c>
       <c r="C2" s="10">
-        <f>Revenue!C6</f>
-        <v>8900</v>
+        <f>Revenue!C7</f>
+        <v>7460</v>
       </c>
       <c r="D2" s="10">
-        <f>Revenue!D6</f>
-        <v>8900</v>
+        <f>Revenue!D7</f>
+        <v>7460</v>
       </c>
       <c r="E2" s="10">
-        <f>Revenue!E6</f>
-        <v>8900</v>
+        <f>Revenue!E7</f>
+        <v>7460</v>
       </c>
       <c r="F2" s="10">
-        <f>Revenue!F6</f>
-        <v>8900</v>
+        <f>Revenue!F7</f>
+        <v>7460</v>
       </c>
       <c r="G2" s="10">
-        <f>Revenue!G6</f>
-        <v>8900</v>
+        <f>Revenue!G7</f>
+        <v>7460</v>
       </c>
       <c r="H2" s="10">
-        <f>Revenue!H6</f>
-        <v>8900</v>
+        <f>Revenue!H7</f>
+        <v>7460</v>
       </c>
       <c r="I2" s="10">
-        <f>Revenue!I6</f>
-        <v>8900</v>
+        <f>Revenue!I7</f>
+        <v>7460</v>
       </c>
       <c r="J2" s="10">
-        <f>Revenue!J6</f>
-        <v>8900</v>
+        <f>Revenue!J7</f>
+        <v>7460</v>
       </c>
       <c r="K2" s="10">
-        <f>Revenue!K6</f>
-        <v>8900</v>
-      </c>
-      <c r="L2" s="10" t="str">
-        <f>Revenue!L6</f>
-        <v>0</v>
+        <f>Revenue!K7</f>
+        <v>7460</v>
+      </c>
+      <c r="L2" s="10">
+        <f>Revenue!L7</f>
+        <v>-1440</v>
       </c>
       <c r="M2" s="10" t="str">
-        <f>Revenue!M6</f>
+        <f>Revenue!M7</f>
         <v>0</v>
       </c>
       <c r="N2" s="10">
         <f>SUM(B2:M2)</f>
-        <v>236000</v>
+        <v>221600</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="7">
         <f>Personnel!B5</f>
@@ -1841,7 +1889,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="7">
         <f>'Operating Expenses'!B8</f>
@@ -1898,52 +1946,52 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="C5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="D5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="E5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="F5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="G5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="H5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="I5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="J5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="K5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="L5" s="7">
-        <v>0</v>
+        <v>580</v>
       </c>
       <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7" t="str">
+        <v>580</v>
+      </c>
+      <c r="N5" s="7">
         <f>SUM(B5:M5)</f>
-        <v>0</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="11" t="str">
         <f>SUM(B3:B5)</f>
@@ -1995,12 +2043,12 @@
       </c>
       <c r="N6" s="11">
         <f>SUM(B6:M6)</f>
-        <v>159434</v>
+        <v>166394</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" s="12" t="str">
         <f>B2-B6</f>
@@ -2052,7 +2100,7 @@
       </c>
       <c r="N7" s="12">
         <f>N2-N6</f>
-        <v>37233</v>
+        <v>18273</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
@@ -179,7 +179,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -194,6 +194,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF1E3A5F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -223,7 +228,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -237,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -257,6 +262,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF93C5FD"/>
       </bottom>
       <diagonal/>
     </border>
@@ -283,18 +297,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
@@ -11,7 +11,7 @@
     <sheet sheetId="5" name="P&amp;L Summary" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$B10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$B11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Revenue'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Revenue'!$1:$1</definedName>
@@ -27,11 +27,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
     <t>School Name</t>
   </si>
   <si>
@@ -57,9 +63,6 @@
   </si>
   <si>
     <t>Year 1 Proration Factor</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>July</t>
@@ -179,7 +182,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -190,6 +193,12 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -293,22 +302,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -651,7 +662,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -664,57 +675,65 @@
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="5">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="6">
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="6">
         <v>0.025</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="7">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -742,327 +761,327 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="9">
         <v>14400</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="9">
         <v>14400</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="9">
         <v>14400</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <v>14400</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="9">
         <v>14400</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="9">
         <v>14400</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="9">
         <v>14400</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="9">
         <v>14400</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="9">
         <v>14400</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="9">
         <v>14400</v>
       </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
+      <c r="L2" s="9">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9">
         <f>SUM(B2:M2)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="7">
-        <v>300</v>
-      </c>
-      <c r="C3" s="7">
-        <v>300</v>
-      </c>
-      <c r="D3" s="7">
-        <v>300</v>
-      </c>
-      <c r="E3" s="7">
-        <v>300</v>
-      </c>
-      <c r="F3" s="7">
-        <v>300</v>
-      </c>
-      <c r="G3" s="7">
-        <v>300</v>
-      </c>
-      <c r="H3" s="7">
-        <v>300</v>
-      </c>
-      <c r="I3" s="7">
-        <v>300</v>
-      </c>
-      <c r="J3" s="7">
-        <v>300</v>
-      </c>
-      <c r="K3" s="7">
-        <v>300</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
+      <c r="A3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="9">
+        <v>300</v>
+      </c>
+      <c r="C3" s="9">
+        <v>300</v>
+      </c>
+      <c r="D3" s="9">
+        <v>300</v>
+      </c>
+      <c r="E3" s="9">
+        <v>300</v>
+      </c>
+      <c r="F3" s="9">
+        <v>300</v>
+      </c>
+      <c r="G3" s="9">
+        <v>300</v>
+      </c>
+      <c r="H3" s="9">
+        <v>300</v>
+      </c>
+      <c r="I3" s="9">
+        <v>300</v>
+      </c>
+      <c r="J3" s="9">
+        <v>300</v>
+      </c>
+      <c r="K3" s="9">
+        <v>300</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
         <f>SUM(B3:M3)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="9">
         <v>8400</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <v>8400</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <v>8400</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <v>8400</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <v>8400</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <v>8400</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <v>8400</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="9">
         <v>8400</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="9">
         <v>8400</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
         <v>8400</v>
       </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
         <f>SUM(B4:M4)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="7">
+      <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="9">
         <v>500</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>500</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>500</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>500</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>500</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>500</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>500</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>500</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>500</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>500</v>
       </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9">
         <f>SUM(B5:M5)</f>
         <v>4167</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="7">
+      <c r="A6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="9">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="9">
         <v>1</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="9">
         <v>1</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="9">
         <v>1</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="9">
         <v>1</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <v>1</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="9">
         <v>1</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="9">
         <v>1</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="9">
         <v>1</v>
       </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
         <f>SUM(B6:M6)</f>
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="8">
+        <v>30</v>
+      </c>
+      <c r="B7" s="10">
         <f>SUM(B2:B6)</f>
         <v>155900</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="10">
         <f>SUM(C2:C6)</f>
         <v>7460</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="10">
         <f>SUM(D2:D6)</f>
         <v>7460</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="10">
         <f>SUM(E2:E6)</f>
         <v>7460</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="10">
         <f>SUM(F2:F6)</f>
         <v>7460</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="10">
         <f>SUM(G2:G6)</f>
         <v>7460</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="10">
         <f>SUM(H2:H6)</f>
         <v>7460</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="10">
         <f>SUM(I2:I6)</f>
         <v>7460</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="10">
         <f>SUM(J2:J6)</f>
         <v>7460</v>
       </c>
-      <c r="K7" s="8">
+      <c r="K7" s="10">
         <f>SUM(K2:K6)</f>
         <v>7460</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="10">
         <f>SUM(L2:L6)</f>
         <v>-1440</v>
       </c>
-      <c r="M7" s="8" t="str">
+      <c r="M7" s="10" t="str">
         <f>SUM(M2:M6)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="8">
+      <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
         <v>221600</v>
       </c>
@@ -1091,237 +1110,237 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="9">
         <v>131313</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="9">
         <v>131313</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="9">
         <v>131313</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <v>131313</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="9">
         <v>131313</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="9">
         <v>131313</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="9">
         <v>131313</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="9">
         <v>131313</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="9">
         <v>131313</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="9">
         <v>131313</v>
       </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
+      <c r="L2" s="9">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9">
         <f>SUM(B2:M2)</f>
         <v>1313125</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9">
         <v>107438</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="9">
         <v>107438</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="9">
         <v>107438</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="9">
         <v>107438</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="9">
         <v>107438</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="9">
         <v>107438</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <v>107438</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="9">
         <v>107438</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="9">
         <v>107438</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="9">
         <v>107438</v>
       </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
         <f>SUM(B3:M3)</f>
         <v>1074375</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="9">
         <v>10092</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <v>10092</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <v>10092</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <v>10092</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <v>10092</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <v>10092</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <v>10092</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="9">
         <v>10092</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="9">
         <v>10092</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
         <v>10092</v>
       </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
         <f>SUM(B4:M4)</f>
         <v>100917</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="8" t="str">
+        <v>34</v>
+      </c>
+      <c r="B5" s="10" t="str">
         <f>SUM(B2:B4)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="8" t="str">
+      <c r="C5" s="10" t="str">
         <f>SUM(C2:C4)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="8" t="str">
+      <c r="D5" s="10" t="str">
         <f>SUM(D2:D4)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="8" t="str">
+      <c r="E5" s="10" t="str">
         <f>SUM(E2:E4)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="8" t="str">
+      <c r="F5" s="10" t="str">
         <f>SUM(F2:F4)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="8" t="str">
+      <c r="G5" s="10" t="str">
         <f>SUM(G2:G4)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="8" t="str">
+      <c r="H5" s="10" t="str">
         <f>SUM(H2:H4)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="8" t="str">
+      <c r="I5" s="10" t="str">
         <f>SUM(I2:I4)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="8" t="str">
+      <c r="J5" s="10" t="str">
         <f>SUM(J2:J4)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="8" t="str">
+      <c r="K5" s="10" t="str">
         <f>SUM(K2:K4)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="8" t="str">
+      <c r="L5" s="10" t="str">
         <f>SUM(L2:L4)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="8" t="str">
+      <c r="M5" s="10" t="str">
         <f>SUM(M2:M4)</f>
         <v>0</v>
       </c>
-      <c r="N5" s="8" t="str">
+      <c r="N5" s="10" t="str">
         <f>SUM(B5:M5)</f>
         <v>0</v>
       </c>
@@ -1350,372 +1369,372 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="9">
         <v>2500</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="9">
         <v>2500</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="9">
         <v>2500</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <v>2500</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="9">
         <v>2500</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="9">
         <v>2500</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="9">
         <v>2500</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="9">
         <v>2500</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="9">
         <v>2500</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="9">
         <v>2500</v>
       </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
+      <c r="L2" s="9">
+        <v>0</v>
+      </c>
+      <c r="M2" s="9">
+        <v>0</v>
+      </c>
+      <c r="N2" s="9">
         <f>SUM(B2:M2)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="7">
-        <v>300</v>
-      </c>
-      <c r="C3" s="7">
-        <v>300</v>
-      </c>
-      <c r="D3" s="7">
-        <v>300</v>
-      </c>
-      <c r="E3" s="7">
-        <v>300</v>
-      </c>
-      <c r="F3" s="7">
-        <v>300</v>
-      </c>
-      <c r="G3" s="7">
-        <v>300</v>
-      </c>
-      <c r="H3" s="7">
-        <v>300</v>
-      </c>
-      <c r="I3" s="7">
-        <v>300</v>
-      </c>
-      <c r="J3" s="7">
-        <v>300</v>
-      </c>
-      <c r="K3" s="7">
-        <v>300</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
+      <c r="A3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="9">
+        <v>300</v>
+      </c>
+      <c r="C3" s="9">
+        <v>300</v>
+      </c>
+      <c r="D3" s="9">
+        <v>300</v>
+      </c>
+      <c r="E3" s="9">
+        <v>300</v>
+      </c>
+      <c r="F3" s="9">
+        <v>300</v>
+      </c>
+      <c r="G3" s="9">
+        <v>300</v>
+      </c>
+      <c r="H3" s="9">
+        <v>300</v>
+      </c>
+      <c r="I3" s="9">
+        <v>300</v>
+      </c>
+      <c r="J3" s="9">
+        <v>300</v>
+      </c>
+      <c r="K3" s="9">
+        <v>300</v>
+      </c>
+      <c r="L3" s="9">
+        <v>0</v>
+      </c>
+      <c r="M3" s="9">
+        <v>0</v>
+      </c>
+      <c r="N3" s="9">
         <f>SUM(B3:M3)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="9">
         <v>200</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <v>200</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <v>200</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <v>200</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <v>200</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <v>200</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <v>200</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="9">
         <v>200</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="9">
         <v>200</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
         <v>200</v>
       </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="9">
         <f>SUM(B4:M4)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="7">
+      <c r="A5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="9">
         <v>500</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>500</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>500</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>500</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>500</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>500</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>500</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>500</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>500</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>500</v>
       </c>
-      <c r="L5" s="7">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0</v>
-      </c>
-      <c r="N5" s="7">
+      <c r="L5" s="9">
+        <v>0</v>
+      </c>
+      <c r="M5" s="9">
+        <v>0</v>
+      </c>
+      <c r="N5" s="9">
         <f>SUM(B5:M5)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="7">
-        <v>300</v>
-      </c>
-      <c r="C6" s="7">
-        <v>300</v>
-      </c>
-      <c r="D6" s="7">
-        <v>300</v>
-      </c>
-      <c r="E6" s="7">
-        <v>300</v>
-      </c>
-      <c r="F6" s="7">
-        <v>300</v>
-      </c>
-      <c r="G6" s="7">
-        <v>300</v>
-      </c>
-      <c r="H6" s="7">
-        <v>300</v>
-      </c>
-      <c r="I6" s="7">
-        <v>300</v>
-      </c>
-      <c r="J6" s="7">
-        <v>300</v>
-      </c>
-      <c r="K6" s="7">
-        <v>300</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
+      <c r="A6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="9">
+        <v>300</v>
+      </c>
+      <c r="C6" s="9">
+        <v>300</v>
+      </c>
+      <c r="D6" s="9">
+        <v>300</v>
+      </c>
+      <c r="E6" s="9">
+        <v>300</v>
+      </c>
+      <c r="F6" s="9">
+        <v>300</v>
+      </c>
+      <c r="G6" s="9">
+        <v>300</v>
+      </c>
+      <c r="H6" s="9">
+        <v>300</v>
+      </c>
+      <c r="I6" s="9">
+        <v>300</v>
+      </c>
+      <c r="J6" s="9">
+        <v>300</v>
+      </c>
+      <c r="K6" s="9">
+        <v>300</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
         <f>SUM(B6:M6)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="7">
+      <c r="A7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="9">
         <v>250</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="9">
         <v>250</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="9">
         <v>250</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <v>250</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="9">
         <v>250</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <v>250</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <v>250</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="9">
         <v>250</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="9">
         <v>250</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="9">
         <v>250</v>
       </c>
-      <c r="L7" s="7">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="7">
+      <c r="L7" s="9">
+        <v>0</v>
+      </c>
+      <c r="M7" s="9">
+        <v>0</v>
+      </c>
+      <c r="N7" s="9">
         <f>SUM(B7:M7)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="8" t="str">
+        <v>41</v>
+      </c>
+      <c r="B8" s="10" t="str">
         <f>SUM(B2:B7)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="8" t="str">
+      <c r="C8" s="10" t="str">
         <f>SUM(C2:C7)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="8" t="str">
+      <c r="D8" s="10" t="str">
         <f>SUM(D2:D7)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="8" t="str">
+      <c r="E8" s="10" t="str">
         <f>SUM(E2:E7)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="8" t="str">
+      <c r="F8" s="10" t="str">
         <f>SUM(F2:F7)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="8" t="str">
+      <c r="G8" s="10" t="str">
         <f>SUM(G2:G7)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="8" t="str">
+      <c r="H8" s="10" t="str">
         <f>SUM(H2:H7)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="8" t="str">
+      <c r="I8" s="10" t="str">
         <f>SUM(I2:I7)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="8" t="str">
+      <c r="J8" s="10" t="str">
         <f>SUM(J2:J7)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="8" t="str">
+      <c r="K8" s="10" t="str">
         <f>SUM(K2:K7)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="8" t="str">
+      <c r="L8" s="10" t="str">
         <f>SUM(L2:L7)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="8" t="str">
+      <c r="M8" s="10" t="str">
         <f>SUM(M2:M7)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="8" t="str">
+      <c r="N8" s="10" t="str">
         <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
@@ -1744,375 +1763,375 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="A1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="G1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="H1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="I1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="J1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="K1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="L1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="M1" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="N1" s="8" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="10">
+      <c r="A2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="12">
         <f>Revenue!B7</f>
         <v>155900</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="12">
         <f>Revenue!C7</f>
         <v>7460</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <f>Revenue!D7</f>
         <v>7460</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="12">
         <f>Revenue!E7</f>
         <v>7460</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="12">
         <f>Revenue!F7</f>
         <v>7460</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="12">
         <f>Revenue!G7</f>
         <v>7460</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="12">
         <f>Revenue!H7</f>
         <v>7460</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <f>Revenue!I7</f>
         <v>7460</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="12">
         <f>Revenue!J7</f>
         <v>7460</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="12">
         <f>Revenue!K7</f>
         <v>7460</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="12">
         <f>Revenue!L7</f>
         <v>-1440</v>
       </c>
-      <c r="M2" s="10" t="str">
+      <c r="M2" s="12" t="str">
         <f>Revenue!M7</f>
         <v>0</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="12">
         <f>SUM(B2:M2)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="7">
+      <c r="A3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="9">
         <f>Personnel!B5</f>
         <v>11893</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="9">
         <f>Personnel!C5</f>
         <v>11893</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="9">
         <f>Personnel!D5</f>
         <v>11893</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="9">
         <f>Personnel!E5</f>
         <v>11893</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="9">
         <f>Personnel!F5</f>
         <v>11893</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="9">
         <f>Personnel!G5</f>
         <v>11893</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <f>Personnel!H5</f>
         <v>11893</v>
       </c>
-      <c r="I3" s="7">
+      <c r="I3" s="9">
         <f>Personnel!I5</f>
         <v>11893</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="9">
         <f>Personnel!J5</f>
         <v>11893</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="9">
         <f>Personnel!K5</f>
         <v>11893</v>
       </c>
-      <c r="L3" s="7" t="str">
+      <c r="L3" s="9" t="str">
         <f>Personnel!L5</f>
         <v>0</v>
       </c>
-      <c r="M3" s="7" t="str">
+      <c r="M3" s="9" t="str">
         <f>Personnel!M5</f>
         <v>0</v>
       </c>
-      <c r="N3" s="7">
+      <c r="N3" s="9">
         <f>SUM(B3:M3)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="7">
+      <c r="A4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="9">
         <f>'Operating Expenses'!B8</f>
         <v>4050</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="9">
         <f>'Operating Expenses'!C8</f>
         <v>4050</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="9">
         <f>'Operating Expenses'!D8</f>
         <v>4050</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="9">
         <f>'Operating Expenses'!E8</f>
         <v>4050</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="9">
         <f>'Operating Expenses'!F8</f>
         <v>4050</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="9">
         <f>'Operating Expenses'!G8</f>
         <v>4050</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <f>'Operating Expenses'!H8</f>
         <v>4050</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="9">
         <f>'Operating Expenses'!I8</f>
         <v>4050</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="9">
         <f>'Operating Expenses'!J8</f>
         <v>4050</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="9">
         <f>'Operating Expenses'!K8</f>
         <v>4050</v>
       </c>
-      <c r="L4" s="7" t="str">
+      <c r="L4" s="9" t="str">
         <f>'Operating Expenses'!L8</f>
         <v>0</v>
       </c>
-      <c r="M4" s="7" t="str">
+      <c r="M4" s="9" t="str">
         <f>'Operating Expenses'!M8</f>
         <v>0</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="9">
         <f>SUM(B4:M4)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="7">
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="9">
         <v>580</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>580</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>580</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>580</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>580</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>580</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>580</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>580</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>580</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>580</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="9">
         <v>580</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="9">
         <v>580</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="9">
         <f>SUM(B5:M5)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="11" t="str">
+        <v>46</v>
+      </c>
+      <c r="B6" s="13" t="str">
         <f>SUM(B3:B5)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="11" t="str">
+      <c r="C6" s="13" t="str">
         <f>SUM(C3:C5)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="11" t="str">
+      <c r="D6" s="13" t="str">
         <f>SUM(D3:D5)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="11" t="str">
+      <c r="E6" s="13" t="str">
         <f>SUM(E3:E5)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="11" t="str">
+      <c r="F6" s="13" t="str">
         <f>SUM(F3:F5)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="11" t="str">
+      <c r="G6" s="13" t="str">
         <f>SUM(G3:G5)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="11" t="str">
+      <c r="H6" s="13" t="str">
         <f>SUM(H3:H5)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="11" t="str">
+      <c r="I6" s="13" t="str">
         <f>SUM(I3:I5)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="11" t="str">
+      <c r="J6" s="13" t="str">
         <f>SUM(J3:J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="11" t="str">
+      <c r="K6" s="13" t="str">
         <f>SUM(K3:K5)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="11" t="str">
+      <c r="L6" s="13" t="str">
         <f>SUM(L3:L5)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="11" t="str">
+      <c r="M6" s="13" t="str">
         <f>SUM(M3:M5)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="11">
+      <c r="N6" s="13">
         <f>SUM(B6:M6)</f>
         <v>166394</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="12" t="str">
+      <c r="A7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="14" t="str">
         <f>B2-B6</f>
         <v>0</v>
       </c>
-      <c r="C7" s="12" t="str">
+      <c r="C7" s="14" t="str">
         <f>C2-C6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="12" t="str">
+      <c r="D7" s="14" t="str">
         <f>D2-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="12" t="str">
+      <c r="E7" s="14" t="str">
         <f>E2-E6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="12" t="str">
+      <c r="F7" s="14" t="str">
         <f>F2-F6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="12" t="str">
+      <c r="G7" s="14" t="str">
         <f>G2-G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="12" t="str">
+      <c r="H7" s="14" t="str">
         <f>H2-H6</f>
         <v>0</v>
       </c>
-      <c r="I7" s="12" t="str">
+      <c r="I7" s="14" t="str">
         <f>I2-I6</f>
         <v>0</v>
       </c>
-      <c r="J7" s="12" t="str">
+      <c r="J7" s="14" t="str">
         <f>J2-J6</f>
         <v>0</v>
       </c>
-      <c r="K7" s="12" t="str">
+      <c r="K7" s="14" t="str">
         <f>K2-K6</f>
         <v>0</v>
       </c>
-      <c r="L7" s="12" t="str">
+      <c r="L7" s="14" t="str">
         <f>L2-L6</f>
         <v>0</v>
       </c>
-      <c r="M7" s="12" t="str">
+      <c r="M7" s="14" t="str">
         <f>M2-M6</f>
         <v>0</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="14">
         <f>N2-N6</f>
         <v>18273</v>
       </c>

--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
@@ -11,7 +11,7 @@
     <sheet sheetId="5" name="P&amp;L Summary" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$B11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$E11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Assumptions'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Revenue'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Revenue'!$1:$1</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>School Name</t>
@@ -223,7 +226,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -242,6 +245,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
@@ -251,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -284,6 +292,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFD0D0D0"/>
       </left>
@@ -302,24 +319,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,7 +680,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -675,65 +693,71 @@
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
+      <c r="A4" s="5" t="s">
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
+      <c r="A5" s="5" t="s">
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="6">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="A9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="7">
         <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7">
         <v>0.025</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="7">
+      <c r="A11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="8">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -761,327 +785,327 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="N1" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="10">
         <v>14400</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <v>14400</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>14400</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>14400</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="10">
         <v>14400</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>14400</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>14400</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>14400</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="10">
         <v>14400</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="10">
         <v>14400</v>
       </c>
-      <c r="L2" s="9">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-      <c r="N2" s="9">
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+      <c r="N2" s="10">
         <f>SUM(B2:M2)</f>
         <v>120000</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="9">
-        <v>300</v>
-      </c>
-      <c r="C3" s="9">
-        <v>300</v>
-      </c>
-      <c r="D3" s="9">
-        <v>300</v>
-      </c>
-      <c r="E3" s="9">
-        <v>300</v>
-      </c>
-      <c r="F3" s="9">
-        <v>300</v>
-      </c>
-      <c r="G3" s="9">
-        <v>300</v>
-      </c>
-      <c r="H3" s="9">
-        <v>300</v>
-      </c>
-      <c r="I3" s="9">
-        <v>300</v>
-      </c>
-      <c r="J3" s="9">
-        <v>300</v>
-      </c>
-      <c r="K3" s="9">
-        <v>300</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9">
+      <c r="A3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="10">
+        <v>300</v>
+      </c>
+      <c r="C3" s="10">
+        <v>300</v>
+      </c>
+      <c r="D3" s="10">
+        <v>300</v>
+      </c>
+      <c r="E3" s="10">
+        <v>300</v>
+      </c>
+      <c r="F3" s="10">
+        <v>300</v>
+      </c>
+      <c r="G3" s="10">
+        <v>300</v>
+      </c>
+      <c r="H3" s="10">
+        <v>300</v>
+      </c>
+      <c r="I3" s="10">
+        <v>300</v>
+      </c>
+      <c r="J3" s="10">
+        <v>300</v>
+      </c>
+      <c r="K3" s="10">
+        <v>300</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
         <f>SUM(B3:M3)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="10">
         <v>8400</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>8400</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <v>8400</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>8400</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <v>8400</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <v>8400</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <v>8400</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <v>8400</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="10">
         <v>8400</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="10">
         <v>8400</v>
       </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
         <f>SUM(B4:M4)</f>
         <v>70000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="10">
         <v>500</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>500</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>500</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>500</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>500</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>500</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>500</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>500</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="10">
         <v>500</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="10">
         <v>500</v>
       </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9">
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
         <f>SUM(B5:M5)</f>
         <v>4167</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="9">
+      <c r="A6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="10">
         <v>1</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="10">
         <v>1</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <v>1</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="10">
         <v>1</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="10">
         <v>1</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="10">
         <v>1</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>1</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="10">
         <v>1</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="10">
         <v>1</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="10">
         <v>1</v>
       </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9">
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
         <v>8</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="10">
+        <v>31</v>
+      </c>
+      <c r="B7" s="11">
         <f>SUM(B2:B6)</f>
         <v>155900</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="11">
         <f>SUM(C2:C6)</f>
         <v>7460</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <f>SUM(D2:D6)</f>
         <v>7460</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="11">
         <f>SUM(E2:E6)</f>
         <v>7460</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="11">
         <f>SUM(F2:F6)</f>
         <v>7460</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="11">
         <f>SUM(G2:G6)</f>
         <v>7460</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="11">
         <f>SUM(H2:H6)</f>
         <v>7460</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="11">
         <f>SUM(I2:I6)</f>
         <v>7460</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="11">
         <f>SUM(J2:J6)</f>
         <v>7460</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="11">
         <f>SUM(K2:K6)</f>
         <v>7460</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="11">
         <f>SUM(L2:L6)</f>
         <v>-1440</v>
       </c>
-      <c r="M7" s="10" t="str">
+      <c r="M7" s="11" t="str">
         <f>SUM(M2:M6)</f>
         <v>0</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="11">
         <f>SUM(B7:M7)</f>
         <v>221600</v>
       </c>
@@ -1110,237 +1134,237 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="N1" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="10">
         <v>131313</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <v>131313</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>131313</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>131313</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="10">
         <v>131313</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>131313</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>131313</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>131313</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="10">
         <v>131313</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="10">
         <v>131313</v>
       </c>
-      <c r="L2" s="9">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-      <c r="N2" s="9">
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+      <c r="N2" s="10">
         <f>SUM(B2:M2)</f>
         <v>1313125</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="A3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="10">
         <v>107438</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <v>107438</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="10">
         <v>107438</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <v>107438</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="10">
         <v>107438</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <v>107438</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <v>107438</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <v>107438</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="10">
         <v>107438</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="10">
         <v>107438</v>
       </c>
-      <c r="L3" s="9">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9">
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
         <f>SUM(B3:M3)</f>
         <v>1074375</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="10">
         <v>10092</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>10092</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <v>10092</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>10092</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <v>10092</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <v>10092</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <v>10092</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <v>10092</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="10">
         <v>10092</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="10">
         <v>10092</v>
       </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
         <f>SUM(B4:M4)</f>
         <v>100917</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="10" t="str">
+        <v>35</v>
+      </c>
+      <c r="B5" s="11" t="str">
         <f>SUM(B2:B4)</f>
         <v>0</v>
       </c>
-      <c r="C5" s="10" t="str">
+      <c r="C5" s="11" t="str">
         <f>SUM(C2:C4)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="10" t="str">
+      <c r="D5" s="11" t="str">
         <f>SUM(D2:D4)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="10" t="str">
+      <c r="E5" s="11" t="str">
         <f>SUM(E2:E4)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="10" t="str">
+      <c r="F5" s="11" t="str">
         <f>SUM(F2:F4)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="10" t="str">
+      <c r="G5" s="11" t="str">
         <f>SUM(G2:G4)</f>
         <v>0</v>
       </c>
-      <c r="H5" s="10" t="str">
+      <c r="H5" s="11" t="str">
         <f>SUM(H2:H4)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="10" t="str">
+      <c r="I5" s="11" t="str">
         <f>SUM(I2:I4)</f>
         <v>0</v>
       </c>
-      <c r="J5" s="10" t="str">
+      <c r="J5" s="11" t="str">
         <f>SUM(J2:J4)</f>
         <v>0</v>
       </c>
-      <c r="K5" s="10" t="str">
+      <c r="K5" s="11" t="str">
         <f>SUM(K2:K4)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="10" t="str">
+      <c r="L5" s="11" t="str">
         <f>SUM(L2:L4)</f>
         <v>0</v>
       </c>
-      <c r="M5" s="10" t="str">
+      <c r="M5" s="11" t="str">
         <f>SUM(M2:M4)</f>
         <v>0</v>
       </c>
-      <c r="N5" s="10" t="str">
+      <c r="N5" s="11" t="str">
         <f>SUM(B5:M5)</f>
         <v>0</v>
       </c>
@@ -1369,372 +1393,372 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="N1" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="10">
         <v>2500</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <v>2500</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="10">
         <v>2500</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="10">
         <v>2500</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="10">
         <v>2500</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2" s="10">
         <v>2500</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="10">
         <v>2500</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="10">
         <v>2500</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="10">
         <v>2500</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="10">
         <v>2500</v>
       </c>
-      <c r="L2" s="9">
-        <v>0</v>
-      </c>
-      <c r="M2" s="9">
-        <v>0</v>
-      </c>
-      <c r="N2" s="9">
+      <c r="L2" s="10">
+        <v>0</v>
+      </c>
+      <c r="M2" s="10">
+        <v>0</v>
+      </c>
+      <c r="N2" s="10">
         <f>SUM(B2:M2)</f>
         <v>25000</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="9">
-        <v>300</v>
-      </c>
-      <c r="C3" s="9">
-        <v>300</v>
-      </c>
-      <c r="D3" s="9">
-        <v>300</v>
-      </c>
-      <c r="E3" s="9">
-        <v>300</v>
-      </c>
-      <c r="F3" s="9">
-        <v>300</v>
-      </c>
-      <c r="G3" s="9">
-        <v>300</v>
-      </c>
-      <c r="H3" s="9">
-        <v>300</v>
-      </c>
-      <c r="I3" s="9">
-        <v>300</v>
-      </c>
-      <c r="J3" s="9">
-        <v>300</v>
-      </c>
-      <c r="K3" s="9">
-        <v>300</v>
-      </c>
-      <c r="L3" s="9">
-        <v>0</v>
-      </c>
-      <c r="M3" s="9">
-        <v>0</v>
-      </c>
-      <c r="N3" s="9">
+      <c r="A3" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="10">
+        <v>300</v>
+      </c>
+      <c r="C3" s="10">
+        <v>300</v>
+      </c>
+      <c r="D3" s="10">
+        <v>300</v>
+      </c>
+      <c r="E3" s="10">
+        <v>300</v>
+      </c>
+      <c r="F3" s="10">
+        <v>300</v>
+      </c>
+      <c r="G3" s="10">
+        <v>300</v>
+      </c>
+      <c r="H3" s="10">
+        <v>300</v>
+      </c>
+      <c r="I3" s="10">
+        <v>300</v>
+      </c>
+      <c r="J3" s="10">
+        <v>300</v>
+      </c>
+      <c r="K3" s="10">
+        <v>300</v>
+      </c>
+      <c r="L3" s="10">
+        <v>0</v>
+      </c>
+      <c r="M3" s="10">
+        <v>0</v>
+      </c>
+      <c r="N3" s="10">
         <f>SUM(B3:M3)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="10">
         <v>200</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <v>200</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <v>200</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <v>200</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <v>200</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <v>200</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <v>200</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <v>200</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="10">
         <v>200</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="10">
         <v>200</v>
       </c>
-      <c r="L4" s="9">
-        <v>0</v>
-      </c>
-      <c r="M4" s="9">
-        <v>0</v>
-      </c>
-      <c r="N4" s="9">
+      <c r="L4" s="10">
+        <v>0</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
         <f>SUM(B4:M4)</f>
         <v>2000</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="10">
         <v>500</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>500</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>500</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>500</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>500</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>500</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>500</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>500</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="10">
         <v>500</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="10">
         <v>500</v>
       </c>
-      <c r="L5" s="9">
-        <v>0</v>
-      </c>
-      <c r="M5" s="9">
-        <v>0</v>
-      </c>
-      <c r="N5" s="9">
+      <c r="L5" s="10">
+        <v>0</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0</v>
+      </c>
+      <c r="N5" s="10">
         <f>SUM(B5:M5)</f>
         <v>5000</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="9">
-        <v>300</v>
-      </c>
-      <c r="C6" s="9">
-        <v>300</v>
-      </c>
-      <c r="D6" s="9">
-        <v>300</v>
-      </c>
-      <c r="E6" s="9">
-        <v>300</v>
-      </c>
-      <c r="F6" s="9">
-        <v>300</v>
-      </c>
-      <c r="G6" s="9">
-        <v>300</v>
-      </c>
-      <c r="H6" s="9">
-        <v>300</v>
-      </c>
-      <c r="I6" s="9">
-        <v>300</v>
-      </c>
-      <c r="J6" s="9">
-        <v>300</v>
-      </c>
-      <c r="K6" s="9">
-        <v>300</v>
-      </c>
-      <c r="L6" s="9">
-        <v>0</v>
-      </c>
-      <c r="M6" s="9">
-        <v>0</v>
-      </c>
-      <c r="N6" s="9">
+      <c r="A6" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="10">
+        <v>300</v>
+      </c>
+      <c r="C6" s="10">
+        <v>300</v>
+      </c>
+      <c r="D6" s="10">
+        <v>300</v>
+      </c>
+      <c r="E6" s="10">
+        <v>300</v>
+      </c>
+      <c r="F6" s="10">
+        <v>300</v>
+      </c>
+      <c r="G6" s="10">
+        <v>300</v>
+      </c>
+      <c r="H6" s="10">
+        <v>300</v>
+      </c>
+      <c r="I6" s="10">
+        <v>300</v>
+      </c>
+      <c r="J6" s="10">
+        <v>300</v>
+      </c>
+      <c r="K6" s="10">
+        <v>300</v>
+      </c>
+      <c r="L6" s="10">
+        <v>0</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0</v>
+      </c>
+      <c r="N6" s="10">
         <f>SUM(B6:M6)</f>
         <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="9">
+      <c r="A7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="10">
         <v>250</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="10">
         <v>250</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="10">
         <v>250</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>250</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="10">
         <v>250</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="10">
         <v>250</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="10">
         <v>250</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="10">
         <v>250</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="10">
         <v>250</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="10">
         <v>250</v>
       </c>
-      <c r="L7" s="9">
-        <v>0</v>
-      </c>
-      <c r="M7" s="9">
-        <v>0</v>
-      </c>
-      <c r="N7" s="9">
+      <c r="L7" s="10">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0</v>
+      </c>
+      <c r="N7" s="10">
         <f>SUM(B7:M7)</f>
         <v>2500</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="10" t="str">
+        <v>42</v>
+      </c>
+      <c r="B8" s="11" t="str">
         <f>SUM(B2:B7)</f>
         <v>0</v>
       </c>
-      <c r="C8" s="10" t="str">
+      <c r="C8" s="11" t="str">
         <f>SUM(C2:C7)</f>
         <v>0</v>
       </c>
-      <c r="D8" s="10" t="str">
+      <c r="D8" s="11" t="str">
         <f>SUM(D2:D7)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="10" t="str">
+      <c r="E8" s="11" t="str">
         <f>SUM(E2:E7)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="10" t="str">
+      <c r="F8" s="11" t="str">
         <f>SUM(F2:F7)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="10" t="str">
+      <c r="G8" s="11" t="str">
         <f>SUM(G2:G7)</f>
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="str">
+      <c r="H8" s="11" t="str">
         <f>SUM(H2:H7)</f>
         <v>0</v>
       </c>
-      <c r="I8" s="10" t="str">
+      <c r="I8" s="11" t="str">
         <f>SUM(I2:I7)</f>
         <v>0</v>
       </c>
-      <c r="J8" s="10" t="str">
+      <c r="J8" s="11" t="str">
         <f>SUM(J2:J7)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="10" t="str">
+      <c r="K8" s="11" t="str">
         <f>SUM(K2:K7)</f>
         <v>0</v>
       </c>
-      <c r="L8" s="10" t="str">
+      <c r="L8" s="11" t="str">
         <f>SUM(L2:L7)</f>
         <v>0</v>
       </c>
-      <c r="M8" s="10" t="str">
+      <c r="M8" s="11" t="str">
         <f>SUM(M2:M7)</f>
         <v>0</v>
       </c>
-      <c r="N8" s="10" t="str">
+      <c r="N8" s="11" t="str">
         <f>SUM(B8:M8)</f>
         <v>0</v>
       </c>
@@ -1763,375 +1787,375 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="F1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="L1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="M1" s="9" t="s">
         <v>24</v>
       </c>
+      <c r="N1" s="9" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="12">
+      <c r="A2" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="13">
         <f>Revenue!B7</f>
         <v>155900</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <f>Revenue!C7</f>
         <v>7460</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="13">
         <f>Revenue!D7</f>
         <v>7460</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="13">
         <f>Revenue!E7</f>
         <v>7460</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="13">
         <f>Revenue!F7</f>
         <v>7460</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="13">
         <f>Revenue!G7</f>
         <v>7460</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="13">
         <f>Revenue!H7</f>
         <v>7460</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <f>Revenue!I7</f>
         <v>7460</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="13">
         <f>Revenue!J7</f>
         <v>7460</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="13">
         <f>Revenue!K7</f>
         <v>7460</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="13">
         <f>Revenue!L7</f>
         <v>-1440</v>
       </c>
-      <c r="M2" s="12" t="str">
+      <c r="M2" s="13" t="str">
         <f>Revenue!M7</f>
         <v>0</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="13">
         <f>SUM(B2:M2)</f>
         <v>221600</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="9">
+      <c r="A3" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="10">
         <f>Personnel!B5</f>
         <v>11893</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>Personnel!C5</f>
         <v>11893</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="10">
         <f>Personnel!D5</f>
         <v>11893</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="10">
         <f>Personnel!E5</f>
         <v>11893</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="10">
         <f>Personnel!F5</f>
         <v>11893</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3" s="10">
         <f>Personnel!G5</f>
         <v>11893</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="10">
         <f>Personnel!H5</f>
         <v>11893</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="10">
         <f>Personnel!I5</f>
         <v>11893</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="10">
         <f>Personnel!J5</f>
         <v>11893</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="10">
         <f>Personnel!K5</f>
         <v>11893</v>
       </c>
-      <c r="L3" s="9" t="str">
+      <c r="L3" s="10" t="str">
         <f>Personnel!L5</f>
         <v>0</v>
       </c>
-      <c r="M3" s="9" t="str">
+      <c r="M3" s="10" t="str">
         <f>Personnel!M5</f>
         <v>0</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="10">
         <f>SUM(B3:M3)</f>
         <v>118934</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="9">
+      <c r="A4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="10">
         <f>'Operating Expenses'!B8</f>
         <v>4050</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <f>'Operating Expenses'!C8</f>
         <v>4050</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="10">
         <f>'Operating Expenses'!D8</f>
         <v>4050</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="10">
         <f>'Operating Expenses'!E8</f>
         <v>4050</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="10">
         <f>'Operating Expenses'!F8</f>
         <v>4050</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4" s="10">
         <f>'Operating Expenses'!G8</f>
         <v>4050</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="10">
         <f>'Operating Expenses'!H8</f>
         <v>4050</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="10">
         <f>'Operating Expenses'!I8</f>
         <v>4050</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="10">
         <f>'Operating Expenses'!J8</f>
         <v>4050</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="10">
         <f>'Operating Expenses'!K8</f>
         <v>4050</v>
       </c>
-      <c r="L4" s="9" t="str">
+      <c r="L4" s="10" t="str">
         <f>'Operating Expenses'!L8</f>
         <v>0</v>
       </c>
-      <c r="M4" s="9" t="str">
+      <c r="M4" s="10" t="str">
         <f>'Operating Expenses'!M8</f>
         <v>0</v>
       </c>
-      <c r="N4" s="9">
+      <c r="N4" s="10">
         <f>SUM(B4:M4)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="9">
+      <c r="A5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="10">
         <v>580</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <v>580</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>580</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="10">
         <v>580</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="10">
         <v>580</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5" s="10">
         <v>580</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>580</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="10">
         <v>580</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="10">
         <v>580</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="10">
         <v>580</v>
       </c>
-      <c r="L5" s="9">
+      <c r="L5" s="10">
         <v>580</v>
       </c>
-      <c r="M5" s="9">
+      <c r="M5" s="10">
         <v>580</v>
       </c>
-      <c r="N5" s="9">
+      <c r="N5" s="10">
         <f>SUM(B5:M5)</f>
         <v>6960</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="13" t="str">
+        <v>47</v>
+      </c>
+      <c r="B6" s="14" t="str">
         <f>SUM(B3:B5)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="13" t="str">
+      <c r="C6" s="14" t="str">
         <f>SUM(C3:C5)</f>
         <v>0</v>
       </c>
-      <c r="D6" s="13" t="str">
+      <c r="D6" s="14" t="str">
         <f>SUM(D3:D5)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="13" t="str">
+      <c r="E6" s="14" t="str">
         <f>SUM(E3:E5)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="13" t="str">
+      <c r="F6" s="14" t="str">
         <f>SUM(F3:F5)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="13" t="str">
+      <c r="G6" s="14" t="str">
         <f>SUM(G3:G5)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="13" t="str">
+      <c r="H6" s="14" t="str">
         <f>SUM(H3:H5)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="13" t="str">
+      <c r="I6" s="14" t="str">
         <f>SUM(I3:I5)</f>
         <v>0</v>
       </c>
-      <c r="J6" s="13" t="str">
+      <c r="J6" s="14" t="str">
         <f>SUM(J3:J5)</f>
         <v>0</v>
       </c>
-      <c r="K6" s="13" t="str">
+      <c r="K6" s="14" t="str">
         <f>SUM(K3:K5)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="13" t="str">
+      <c r="L6" s="14" t="str">
         <f>SUM(L3:L5)</f>
         <v>0</v>
       </c>
-      <c r="M6" s="13" t="str">
+      <c r="M6" s="14" t="str">
         <f>SUM(M3:M5)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="13">
+      <c r="N6" s="14">
         <f>SUM(B6:M6)</f>
         <v>166394</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="14" t="str">
+      <c r="A7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="15" t="str">
         <f>B2-B6</f>
         <v>0</v>
       </c>
-      <c r="C7" s="14" t="str">
+      <c r="C7" s="15" t="str">
         <f>C2-C6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="14" t="str">
+      <c r="D7" s="15" t="str">
         <f>D2-D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="14" t="str">
+      <c r="E7" s="15" t="str">
         <f>E2-E6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="14" t="str">
+      <c r="F7" s="15" t="str">
         <f>F2-F6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="14" t="str">
+      <c r="G7" s="15" t="str">
         <f>G2-G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="14" t="str">
+      <c r="H7" s="15" t="str">
         <f>H2-H6</f>
         <v>0</v>
       </c>
-      <c r="I7" s="14" t="str">
+      <c r="I7" s="15" t="str">
         <f>I2-I6</f>
         <v>0</v>
       </c>
-      <c r="J7" s="14" t="str">
+      <c r="J7" s="15" t="str">
         <f>J2-J6</f>
         <v>0</v>
       </c>
-      <c r="K7" s="14" t="str">
+      <c r="K7" s="15" t="str">
         <f>K2-K6</f>
         <v>0</v>
       </c>
-      <c r="L7" s="14" t="str">
+      <c r="L7" s="15" t="str">
         <f>L2-L6</f>
         <v>0</v>
       </c>
-      <c r="M7" s="14" t="str">
+      <c r="M7" s="15" t="str">
         <f>M2-M6</f>
         <v>0</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="15">
         <f>N2-N6</f>
         <v>18273</v>
       </c>

--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
@@ -328,7 +328,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>

--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_Startup.xlsx
@@ -9,6 +9,7 @@
     <sheet sheetId="3" name="Personnel" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Operating Expenses" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="P&amp;L Summary" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Decision History" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$E11</definedName>
@@ -21,13 +22,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'P&amp;L Summary'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'P&amp;L Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Decision History'!$A1:$H4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Decision History'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="52">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
@@ -174,6 +177,15 @@
   </si>
   <si>
     <t>Profit / (Loss)</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -185,7 +197,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -223,6 +235,24 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -319,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -338,6 +368,13 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2168,4 +2205,71 @@
     <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>